--- a/03_Problem3_Expected_Credit_Loss_IFRS9_CECL/reports/financial_impact_reporting_packaging/AMEX_Problem3_Financial_Impact_Workbook.xlsx
+++ b/03_Problem3_Expected_Credit_Loss_IFRS9_CECL/reports/financial_impact_reporting_packaging/AMEX_Problem3_Financial_Impact_Workbook.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -177,6 +177,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -838,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A2:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -848,7 +849,6 @@
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -975,6 +975,30 @@
       <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Rows 5-10 recalculate live from the Standard Comparison, Macro Sensitivity, and Assumptions sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Business Impact — Modeled Estimate, Not Audited Value</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The $4,617,593 IFRS9-vs-flat reserve change and $603,424 CECL-vs-IFRS9 day-one delta are self-computed under this report's own documented staging/LGD assumptions -- they have not been audited by a third party or realized as an actual regulatory capital or reserve outcome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>Independent Audit Status</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>This project was developed as an independent portfolio body of work and has not undergone formal validation, audit, or sign-off by a financial institution's model risk management (SR 11-7 or equivalent) function, a third-party auditor, or a regulator. All model outputs, risk metrics, and business-impact figures in this report are self-computed under the assumptions stated herein and have not been realized in a live production environment at a financial institution.</t>
         </is>
       </c>
     </row>
